--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8467-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8467-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{198D7707-375D-40A2-87D1-67A1045E7197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD0BE555-3618-43D1-9291-96FF6560A3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{B97F2B1D-D3F7-45A7-839B-0C3C94F1A917}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{005B5489-03FA-4D9E-9FFC-A028E9765978}"/>
   </bookViews>
   <sheets>
     <sheet name="8467-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1478,30 +1478,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64E90B2E-4F4F-4E76-94B5-57006C67B0C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EE8B9A-20A8-4C7B-9DCB-EB10ED7228FE}">
   <dimension ref="A1:X46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1535,7 +1535,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1571,7 +1571,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1691,7 +1691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>28</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2024</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>28</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>28</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>28</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2023</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>28</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>28</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>28</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>28</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>28</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>28</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2021</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>28</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>28</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>28</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>28</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>28</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2020</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>28</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>28</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>28</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>28</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>28</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>28</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2019</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>28</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>28</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>28</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2018</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>2017</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>2016</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>4.8899999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>2015</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>2014</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
         <v>47</v>
       </c>
